--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260626.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260626.xlsx
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2,922,000</t>
+          <t>13,112,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>13,112,000</t>
+          <t>2,922,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>16,869,000</t>
+          <t>9,865,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,171,000</t>
+          <t>16,869,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,865,000</t>
+          <t>2,171,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>6,990,000</t>
+          <t>2,615,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>2,615,000</t>
+          <t>6,990,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
